--- a/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887-detailed.xlsx
+++ b/rtss-pre1917/src/main/resources/ugvi/year-volumes/1887-detailed.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\ugvi\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A90AF7BA-BEC9-444E-9296-F1E3A5740F06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84DDE8F1-A675-450A-A888-6618655ACBFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80505" yWindow="570" windowWidth="26355" windowHeight="18555" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notes" sheetId="2" r:id="rId1"/>
@@ -732,9 +732,6 @@
     <t>Самаркандская обл.</t>
   </si>
   <si>
-    <t>Туркестанская обл.</t>
-  </si>
-  <si>
     <t>Уральская обл.</t>
   </si>
   <si>
@@ -794,6 +791,9 @@
   </si>
   <si>
     <t>Кубанская обл. без Черном.</t>
+  </si>
+  <si>
+    <t>Тургайская обл.</t>
   </si>
 </sst>
 </file>
@@ -998,7 +998,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1236,12 +1236,11 @@
     <xf numFmtId="3" fontId="6" fillId="20" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1413,7 +1412,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
   </sheetData>
@@ -1455,41 +1454,41 @@
         <v>3</v>
       </c>
       <c r="E1" s="3"/>
-      <c r="F1" s="91" t="s">
+      <c r="F1" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="92"/>
-      <c r="H1" s="92"/>
-      <c r="I1" s="92"/>
-      <c r="J1" s="92"/>
-      <c r="K1" s="92"/>
-      <c r="L1" s="92"/>
-      <c r="M1" s="92"/>
-      <c r="N1" s="92"/>
-      <c r="O1" s="92"/>
-      <c r="P1" s="92"/>
-      <c r="Q1" s="92"/>
-      <c r="R1" s="92"/>
-      <c r="S1" s="92"/>
-      <c r="T1" s="92"/>
+      <c r="G1" s="93"/>
+      <c r="H1" s="93"/>
+      <c r="I1" s="93"/>
+      <c r="J1" s="93"/>
+      <c r="K1" s="93"/>
+      <c r="L1" s="93"/>
+      <c r="M1" s="93"/>
+      <c r="N1" s="93"/>
+      <c r="O1" s="93"/>
+      <c r="P1" s="93"/>
+      <c r="Q1" s="93"/>
+      <c r="R1" s="93"/>
+      <c r="S1" s="93"/>
+      <c r="T1" s="93"/>
       <c r="V1" s="81" t="s">
+        <v>243</v>
+      </c>
+      <c r="W1" s="81" t="s">
         <v>244</v>
       </c>
-      <c r="W1" s="81" t="s">
+      <c r="X1" s="81" t="s">
         <v>245</v>
-      </c>
-      <c r="X1" s="81" t="s">
-        <v>246</v>
       </c>
       <c r="Y1" s="81"/>
       <c r="Z1" s="81" t="s">
+        <v>246</v>
+      </c>
+      <c r="AA1" s="81" t="s">
         <v>247</v>
       </c>
-      <c r="AA1" s="81" t="s">
+      <c r="AB1" s="81" t="s">
         <v>248</v>
-      </c>
-      <c r="AB1" s="81" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="14.4" x14ac:dyDescent="0.4">
@@ -3072,7 +3071,7 @@
     </row>
     <row r="32" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A32" s="26" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B32" s="27">
         <v>1307</v>
@@ -3137,7 +3136,7 @@
     </row>
     <row r="33" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A33" s="30" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -3178,7 +3177,7 @@
     </row>
     <row r="34" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A34" s="30" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -3219,7 +3218,7 @@
     </row>
     <row r="35" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A35" s="26" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B35" s="27">
         <v>2424</v>
@@ -3298,7 +3297,7 @@
     </row>
     <row r="36" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A36" s="30" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B36" s="12"/>
       <c r="C36" s="12"/>
@@ -3353,7 +3352,7 @@
     </row>
     <row r="37" spans="1:33" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A37" s="30" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B37" s="12"/>
       <c r="C37" s="12"/>
@@ -5359,7 +5358,7 @@
         <v>393</v>
       </c>
       <c r="C76" s="38">
-        <v>11833</v>
+        <v>11838</v>
       </c>
       <c r="D76" s="38">
         <v>8161</v>
@@ -5406,7 +5405,7 @@
       </c>
       <c r="AA76" s="82">
         <f t="shared" ref="AA76" si="76">C76-W76</f>
-        <v>-3</v>
+        <v>2</v>
       </c>
       <c r="AB76" s="82">
         <f t="shared" ref="AB76" si="77">D76-X76</f>
@@ -5479,7 +5478,7 @@
     </row>
     <row r="79" spans="1:33" ht="24.6" x14ac:dyDescent="0.4">
       <c r="A79" s="86" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B79" s="60">
         <v>10619</v>
@@ -11863,7 +11862,7 @@
     </row>
     <row r="197" spans="1:28" x14ac:dyDescent="0.4">
       <c r="A197" s="51" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B197" s="55">
         <v>1269</v>
@@ -11903,9 +11902,9 @@
         <v>54888</v>
       </c>
     </row>
-    <row r="198" spans="1:28" s="93" customFormat="1" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:28" s="1" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A198" s="51" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B198" s="55">
         <v>18</v>
@@ -11932,15 +11931,15 @@
       <c r="R198" s="52"/>
       <c r="S198" s="52"/>
       <c r="T198" s="52"/>
-      <c r="V198" s="94">
+      <c r="V198" s="91">
         <f>B198</f>
         <v>18</v>
       </c>
-      <c r="W198" s="94">
+      <c r="W198" s="91">
         <f>C198</f>
         <v>706</v>
       </c>
-      <c r="X198" s="94">
+      <c r="X198" s="91">
         <f>D198</f>
         <v>468</v>
       </c>
@@ -13713,7 +13712,7 @@
     </row>
     <row r="237" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A237" s="72" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="B237" s="73">
         <v>343</v>
@@ -13755,7 +13754,7 @@
     </row>
     <row r="238" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A238" s="72" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B238" s="73">
         <v>547</v>
@@ -13797,7 +13796,7 @@
     </row>
     <row r="239" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A239" s="72" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B239" s="73">
         <v>716</v>
@@ -13839,7 +13838,7 @@
     </row>
     <row r="240" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A240" s="75" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B240" s="76">
         <v>5728</v>
@@ -13900,7 +13899,7 @@
     </row>
     <row r="241" spans="1:33" x14ac:dyDescent="0.4">
       <c r="A241" s="75" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B241" s="76">
         <v>110483</v>
